--- a/Main/AUT_EEC_results/AUT_EEC_SIDIS_a0.01_b0.01_x0.30_Q80_LO.xlsx
+++ b/Main/AUT_EEC_results/AUT_EEC_SIDIS_a0.01_b0.01_x0.30_Q80_LO.xlsx
@@ -455,10 +455,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02635657963417057</v>
+        <v>0.01302968678172671</v>
       </c>
       <c r="C2" t="n">
-        <v>0.02635657963417057</v>
+        <v>0.01302968678172671</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -469,10 +469,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.04912947408415347</v>
+        <v>0.02501320450562308</v>
       </c>
       <c r="C3" t="n">
-        <v>0.04912947408415347</v>
+        <v>0.02501320450562308</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -483,10 +483,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.1022004377224572</v>
+        <v>0.05185432327114342</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1022004377224572</v>
+        <v>0.05185432327114342</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -497,10 +497,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.1741061998059645</v>
+        <v>0.08856054720130944</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1741061998059645</v>
+        <v>0.08856054720130944</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -511,10 +511,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.2129423796858303</v>
+        <v>0.1083510016474258</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2129423796858303</v>
+        <v>0.1083510016474258</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -525,10 +525,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.207980414179894</v>
+        <v>0.1056177064174052</v>
       </c>
       <c r="C7" t="n">
-        <v>0.207980414179894</v>
+        <v>0.1056177064174052</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -539,10 +539,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.186634631917398</v>
+        <v>0.09485464345580132</v>
       </c>
       <c r="C8" t="n">
-        <v>0.186634631917398</v>
+        <v>0.09485464345580132</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -553,10 +553,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.1725301232902657</v>
+        <v>0.0878125581140098</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1725301232902657</v>
+        <v>0.0878125581140098</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -567,10 +567,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.1715606350828716</v>
+        <v>0.08744308872971283</v>
       </c>
       <c r="C10" t="n">
-        <v>0.1715606350828716</v>
+        <v>0.08744308872971283</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -581,10 +581,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0.1566526359788847</v>
+        <v>0.07984982657895832</v>
       </c>
       <c r="C11" t="n">
-        <v>0.1566526359788847</v>
+        <v>0.07984982657895832</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
